--- a/templates/testfaelle_pain001_comprehensive_sps.xlsx
+++ b/templates/testfaelle_pain001_comprehensive_sps.xlsx
@@ -1435,17 +1435,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Domestic IBAN falsche Waehrung</t>
+          <t>EUR an CH-IBAN (Grenzueberschreitend)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EUR statt CHF</t>
+          <t>Positiv: EUR an CH-IBAN ist SPS-konform (Zahlungsart 5)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NOK</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CHF</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>BR-IBAN-004</t>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>SPS 2025 erlaubt Fremdwaehrung an CH/LI-IBAN. Der SPS-Validator klassifiziert solche Zahlungen empirisch als Zahlungsart 5 (Grenzueberschreitend), nicht als D/IBAN. Keine Scheme-Regel verletzt.</t>
         </is>
       </c>
     </row>
